--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10418,23 +10409,19 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>35047</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10443,12 +10430,12 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
@@ -10458,7 +10445,7 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19745,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19768,7 +19755,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19932,12 +19919,12 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1070呎 (3房)
-招标单位
--
-(在售)</t>
+$3750万
+$35,047/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -10414,7 +10414,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -19924,7 +19924,7 @@
           <t>A | 1070呎 (3房)
 $3750万
 $35,047/呎
-(26年-09月-07日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +271,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1419,7 +1428,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1083</v>
+        <v>1070</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1444,7 @@
         <v>522621000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>482568</v>
+        <v>488431</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1757,7 +1766,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1767,12 +1776,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1782,12 +1791,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1797,7 +1806,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18349,27 +18358,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -18494,9 +18503,9 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 1083呎 (3房)
+          <t>B | 1070呎 (3房)
 $52262万
-$482,568/呎
+$488,431/呎
 (04年-11月-12日)</t>
         </is>
       </c>
@@ -18523,7 +18532,124 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3680万
+$34,393/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2550万
+$29,825/呎
+(26年-02月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3467万
+$32,956/呎
+(16年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3130万
+$29,252/呎
+(11年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2866万
+$33,518/呎
+(15年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2643万
+$30,917/呎
+(15年-11月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$52262万
+$488,431/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1052呎 (3房)
 -
@@ -18531,15 +18657,132 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 1070呎 (3房)
-$3680万
-$34,393/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
+$3250万
+$30,374/呎
+(26年-03月-05日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2830万
+$33,099/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2620万
+$30,643/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$52262万
+$488,431/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3426万
+$32,564/呎
+(16年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$2950万
+$27,239/呎
+(11年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2833万
+$33,133/呎
+(16年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2640万
+$30,871/呎
+(16年-11月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3100万
+$29,468/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3418万
+$31,944/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 855呎 (3房)
 -
@@ -18547,240 +18790,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2550万
-$29,825/呎
-(26年-02月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3467万
-$32,956/呎
-(16年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3130万
-$29,252/呎
-(11年-02月-21日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2866万
-$33,518/呎
-(15年-10月-19日)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2643万
-$30,917/呎
-(15年-11月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52262万
-$488,431/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3250万
-$30,374/呎
-(26年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2830万
-$33,099/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2620万
-$30,643/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52262万
-$488,431/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 879呎 (3房)
-$52262万
-$594,563/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3426万
-$32,564/呎
-(16年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1083呎 (3房)
-$2950万
-$27,239/呎
-(11年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2833万
-$33,133/呎
-(16年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2640万
-$30,871/呎
-(16年-11月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3100万
-$29,468/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3418万
-$31,944/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 855呎 (3房)
@@ -19654,7 +19663,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr"/>
+      <c r="B37" s="23" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 1042呎 (3房)
@@ -19671,7 +19680,7 @@
 (15年-11月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr"/>
+      <c r="E37" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21097,8 +21106,8 @@
 (01年-12月-29日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr"/>
-      <c r="D38" s="22" t="inlineStr"/>
+      <c r="C38" s="23" t="inlineStr"/>
+      <c r="D38" s="23" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -271,9 +265,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1766,23 +1757,19 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>32800000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>31179</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1791,12 +1778,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1806,7 +1793,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18345,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18368,7 +18355,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18532,12 +18519,12 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1052呎 (3房)
-招标单位
--
-(在售)</t>
+$3280万
+$31,179/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -19663,7 +19650,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr"/>
+      <c r="B37" s="22" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 1042呎 (3房)
@@ -19680,7 +19667,7 @@
 (15年-11月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr"/>
+      <c r="E37" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21106,8 +21093,8 @@
 (01年-12月-29日)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr"/>
-      <c r="D38" s="23" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +271,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5225,7 +5234,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5235,12 +5244,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -5250,12 +5259,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -5265,7 +5274,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18345,27 +18354,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19035,124 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2750万
+$26,141/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$2370万
+$27,399/呎
+(26年-03月-04日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$2280万
+$22,093/呎
+(11年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1065呎 (3房)
+$2553万
+$23,972/呎
+(11年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2578万
+$30,649/呎
+(15年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$2339万
+$27,842/呎
+(16年-06月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1032呎 (3房)
 -
@@ -19034,77 +19160,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 1052呎 (3房)
-$2750万
-$26,141/呎
-(26年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 865呎 (3房)
-$2370万
-$27,399/呎
-(26年-03月-04日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$2800万
+$26,616/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2350万
+$27,943/呎
+(26年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$2280万
-$22,093/呎
-(11年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 1065呎 (3房)
-$2553万
-$23,972/呎
-(11年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2578万
-$30,649/呎
-(15年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$2339万
-$27,842/呎
-(16年-06月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+$889万
+$10,585/呎
+(02年-01月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1032呎 (3房)
 $52262万
@@ -19112,7 +19199,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 1052呎 (3房)
 $52262万
@@ -19120,7 +19207,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 841呎 (3房)
 $52262万
@@ -19128,7 +19215,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)
 $52262万
@@ -19137,13 +19224,169 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$894万
+$10,637/呎
+(02年-02月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$998万
+$9,671/呎
+(01年-12月-29日)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2680万
+$25,720/呎
+(26年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2370万
+$28,181/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$843万
+$10,032/呎
+(01年-12月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 1032呎 (3房)
 -
@@ -19151,54 +19394,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2800万
-$26,616/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2350万
-$27,943/呎
-(26年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$889万
-$10,585/呎
-(02年-01月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1056呎 (3房)
 $52262万
-$506,416/呎
+$494,906/呎
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 841呎 (3房)
 $52262万
@@ -19206,7 +19410,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)
 $52262万
@@ -19215,201 +19419,6 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 1064呎 (3房)
-$52262万
-$491,185/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 865呎 (3房)
-$52262万
-$604,186/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$894万
-$10,637/呎
-(02年-02月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$998万
-$9,671/呎
-(01年-12月-29日)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2680万
-$25,720/呎
-(26年-03月-03日)</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2370万
-$28,181/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$843万
-$10,032/呎
-(01年-12月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 1056呎 (3房)
-$52262万
-$494,906/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
@@ -19650,7 +19659,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr"/>
+      <c r="B37" s="23" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 1042呎 (3房)
@@ -19667,7 +19676,7 @@
 (15年-11月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr"/>
+      <c r="E37" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21093,8 +21102,8 @@
 (01年-12月-29日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr"/>
-      <c r="D38" s="22" t="inlineStr"/>
+      <c r="C38" s="23" t="inlineStr"/>
+      <c r="D38" s="23" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -271,9 +265,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5234,23 +5225,19 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>29264</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5259,12 +5246,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -5274,7 +5261,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18354,7 +18341,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18364,7 +18351,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19035,12 +19022,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1032呎 (3房)
-招标单位
--
-(在售)</t>
+$3020万
+$29,264/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -19659,7 +19646,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr"/>
+      <c r="B37" s="22" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 1042呎 (3房)
@@ -19676,7 +19663,7 @@
 (15年-11月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr"/>
+      <c r="E37" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21102,8 +21089,8 @@
 (01年-12月-29日)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr"/>
-      <c r="D38" s="23" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1709</v>
+        <v>1722</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>63000000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>36864</v>
+        <v>36585</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1437</v>
+        <v>1722</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2093</v>
+        <v>2357</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>105280000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>50301</v>
+        <v>44667</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2059</v>
+        <v>2338</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>88880000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>43167</v>
+        <v>38015</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>522621000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>522621000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>522621000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>488431</v>
+        <v>482568</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>522621000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>522621000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>488431</v>
+        <v>482568</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>522621000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>496788</v>
+        <v>493971</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>25500000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>29825</v>
+        <v>29010</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>36800000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>34393</v>
+        <v>33980</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>32800000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>31179</v>
+        <v>31002</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>26434350</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>30917</v>
+        <v>30073</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>28657800</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>33518</v>
+        <v>32603</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>31300000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>29252</v>
+        <v>28901</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>34669350</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>32956</v>
+        <v>32769</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>522621000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>522621000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>522621000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>488431</v>
+        <v>482568</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>522621000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>496788</v>
+        <v>493971</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>26200000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>30643</v>
+        <v>29807</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>28300000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>33099</v>
+        <v>32196</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>32500000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>30374</v>
+        <v>30009</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>522621000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>611253</v>
+        <v>594563</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>522621000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>488431</v>
+        <v>482568</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>522621000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>496788</v>
+        <v>493971</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>26395005</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>30871</v>
+        <v>30028</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>28328400</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>33133</v>
+        <v>32228</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>34257600</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>32564</v>
+        <v>32380</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>24300000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>28421</v>
+        <v>27645</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>34180000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>31944</v>
+        <v>31560</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>31000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>29468</v>
+        <v>29301</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>522621000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>522621000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>522621000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>522621000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>522621000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>522621000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>496788</v>
+        <v>491185</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>522621000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>522621000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>522621000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>496788</v>
+        <v>491185</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>522621000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>12691000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>12064</v>
+        <v>11928</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>25500000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>30321</v>
+        <v>29480</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>12551000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>11931</v>
+        <v>11796</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>30300000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>29360</v>
+        <v>29163</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>10075000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>11994</v>
+        <v>11647</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>13050000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>12405</v>
+        <v>12265</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>27500000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>26141</v>
+        <v>25846</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>30200000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>29264</v>
+        <v>29066</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>23387400</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>27842</v>
+        <v>27037</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>25775550</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>30649</v>
+        <v>29798</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>25530000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>23972</v>
+        <v>23994</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>22800000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>22093</v>
+        <v>21944</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>522621000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>622168</v>
+        <v>604186</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>522621000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>522621000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>496788</v>
+        <v>491185</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>522621000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>8891000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>10585</v>
+        <v>10279</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>23500000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>27943</v>
+        <v>27168</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>28000000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>26616</v>
+        <v>26316</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>522621000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>622168</v>
+        <v>604186</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>522621000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>522621000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>496788</v>
+        <v>491185</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>522621000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>522621000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>622168</v>
+        <v>604186</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>522621000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>522621000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>622168</v>
+        <v>604186</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>522621000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>522621000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>496788</v>
+        <v>491185</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>522621000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>8935000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>10637</v>
+        <v>10329</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>522621000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>506416</v>
+        <v>503004</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>8427000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>10032</v>
+        <v>9742</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>23700000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>28181</v>
+        <v>27399</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>26800000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>25720</v>
+        <v>25379</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>9980000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>9671</v>
+        <v>9605</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>522621000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>622168</v>
+        <v>604186</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>522621000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>621428</v>
+        <v>604186</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>7600000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>9048</v>
+        <v>8786</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>19600000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>23306</v>
+        <v>22659</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>20880000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>20038</v>
+        <v>19773</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>5495000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>8863</v>
+        <v>8877</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>16700000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>19881</v>
+        <v>19306</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>20834550</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>24774</v>
+        <v>24086</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>10490000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>10067</v>
+        <v>9934</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>4646000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>7518</v>
+        <v>7506</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>7850000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>9345</v>
+        <v>9075</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>8810000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>10476</v>
+        <v>10185</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>21880000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>20998</v>
+        <v>20720</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>4820000</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>7799</v>
+        <v>7787</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>6897000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>8211</v>
+        <v>7973</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>20340450</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>24186</v>
+        <v>23515</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>22100000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>21209</v>
+        <v>20928</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>5290000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>8560</v>
+        <v>8546</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>7301000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>8692</v>
+        <v>8440</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>20399925</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>24257</v>
+        <v>23584</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>5200000</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>8414</v>
+        <v>8401</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>6622000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>7883</v>
+        <v>7655</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>47186550</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>56108</v>
+        <v>54551</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>522621000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>501556</v>
+        <v>494906</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>4332000</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>7010</v>
+        <v>6998</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>841</v>
+        <v>867</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>19105200</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>22717</v>
+        <v>22036</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>25610850</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>24579</v>
+        <v>24253</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>1366</v>
+        <v>1722</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>33300000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>24378</v>
+        <v>19338</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>1366</v>
+        <v>1722</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>29628000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>21690</v>
+        <v>17206</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1995</v>
+        <v>2299</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>43000000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>21554</v>
+        <v>18704</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2010</v>
+        <v>2295</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>1412</v>
+        <v>1532</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>61103700</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>43275</v>
+        <v>39885</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1412</v>
+        <v>1532</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>29800000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>21105</v>
+        <v>19452</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>2158</v>
+        <v>2176</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>2181</v>
+        <v>2201</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>76177000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>34928</v>
+        <v>34610</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>24100000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>28187</v>
+        <v>27418</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>27977040</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>32722</v>
+        <v>31828</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>34422300</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>32721</v>
+        <v>32535</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>29000000</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>27103</v>
+        <v>26777</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>25900000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>30292</v>
+        <v>29465</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>33000000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>31369</v>
+        <v>31191</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>37500000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>35047</v>
+        <v>34626</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>13630000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>12738</v>
+        <v>12585</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>28500000</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>33333</v>
+        <v>32423</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>25112000</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>29371</v>
+        <v>28569</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>27888000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>26510</v>
+        <v>26359</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>38600000</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>36075</v>
+        <v>35642</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>26300000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>30760</v>
+        <v>29920</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>27000000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>31579</v>
+        <v>30717</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>26628000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>25312</v>
+        <v>25168</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>29250000</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>27336</v>
+        <v>27008</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>26187300</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>30628</v>
+        <v>29792</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>26846100</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>31399</v>
+        <v>30542</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>25800000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>24525</v>
+        <v>24386</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>26500000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>24766</v>
+        <v>24469</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>26022600</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>30436</v>
+        <v>29605</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>47186550</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>55189</v>
+        <v>53682</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>25200000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>23954</v>
+        <v>23819</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>22650000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>26491</v>
+        <v>25768</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>26846100</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>31399</v>
+        <v>30542</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>33722325</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>32055</v>
+        <v>31874</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>27150000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>25374</v>
+        <v>25069</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>9881000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>11557</v>
+        <v>11241</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>25600000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>30440</v>
+        <v>29595</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>17919000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>21307</v>
+        <v>20716</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>24480000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>23721</v>
+        <v>23561</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>33763500</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>32095</v>
+        <v>31733</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>21540000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>25612</v>
+        <v>24902</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>20800000</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>24732</v>
+        <v>24046</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>22500000</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>21802</v>
+        <v>21655</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>11924000</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>11335</v>
+        <v>11207</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>22100000</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>21415</v>
+        <v>21270</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>23500000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>22066</v>
+        <v>22086</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>21180000</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>25184</v>
+        <v>24486</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>20830000</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>24768</v>
+        <v>24081</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>21600000</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>20930</v>
+        <v>20789</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>11670000</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>11093</v>
+        <v>10968</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>23799150</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>28299</v>
+        <v>27513</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>19600000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>23333</v>
+        <v>22659</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>21600000</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>20809</v>
+        <v>20789</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>12105000</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>11507</v>
+        <v>11377</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>20000000</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>23781</v>
+        <v>23121</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>19900000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>23690</v>
+        <v>23006</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>30280000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>29341</v>
+        <v>29143</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>11970000</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>11378</v>
+        <v>11250</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>9464000</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>11253</v>
+        <v>10941</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>19000000</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>22619</v>
+        <v>21965</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>21000000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>20349</v>
+        <v>20212</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>23634450</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>28103</v>
+        <v>27323</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>19900000</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>23690</v>
+        <v>23006</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>21400000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>20617</v>
+        <v>20597</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>11396000</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>10833</v>
+        <v>10711</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>9460000</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>11249</v>
+        <v>10936</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>9527000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>9232</v>
+        <v>9169</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>10153000</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>9651</v>
+        <v>9542</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>8956000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>10649</v>
+        <v>10354</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>19500000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>18895</v>
+        <v>18768</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>10639000</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>10113</v>
+        <v>9999</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>18380000</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>21855</v>
+        <v>21249</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>18100000</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>20973</v>
+        <v>20925</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>19380000</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>18779</v>
+        <v>18653</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>17900000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>21284</v>
+        <v>20694</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>17400000</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>20714</v>
+        <v>20116</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>19000000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>18411</v>
+        <v>18287</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>9130000</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>10856</v>
+        <v>10555</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>18673000</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>18094</v>
+        <v>17972</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>9423000</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>8848</v>
+        <v>8856</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>7334000</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>8721</v>
+        <v>8479</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>8813000</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>10492</v>
+        <v>10188</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>19180000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>18585</v>
+        <v>18460</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>10650000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>10221</v>
+        <v>10085</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>17800000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>21190</v>
+        <v>20578</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>10149000</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>9740</v>
+        <v>9611</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>7505000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>8935</v>
+        <v>8676</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>8400000</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>8140</v>
+        <v>8085</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>7331000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>8717</v>
+        <v>8475</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>7910000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>9417</v>
+        <v>9145</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>4870000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>7880</v>
+        <v>7868</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="E244" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>8580000</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>8234</v>
+        <v>8125</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>841</v>
+        <v>865</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>7149000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>8501</v>
+        <v>8265</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>7230000</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>8607</v>
+        <v>8358</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>8907000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>8548</v>
+        <v>8435</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>7094000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>8445</v>
+        <v>8201</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>4810000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>7783</v>
+        <v>7771</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>8281000</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>7947</v>
+        <v>7842</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>14900000</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>17738</v>
+        <v>17225</v>
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>6498000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>7736</v>
+        <v>7512</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>4260000</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>6893</v>
+        <v>6882</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>8660000</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>8311</v>
+        <v>8201</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>7180000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>8548</v>
+        <v>8301</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>7245000</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>8625</v>
+        <v>8376</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>4564000</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>7385</v>
+        <v>7373</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>6666000</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>7936</v>
+        <v>7706</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>7070000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>8417</v>
+        <v>8173</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>3734000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>6042</v>
+        <v>6032</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>7601000</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>7295</v>
+        <v>7198</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>6615000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>7875</v>
+        <v>7630</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>7317000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>7022</v>
+        <v>6929</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -18400,23 +18400,23 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2059呎 (3房)
+          <t>A | 2338呎 (3房)
 $8888万
-$43,167/呎
+$38,015/呎
 (16年-09月-02日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 2093呎 (3房)
+          <t>B | 2357呎 (3房)
 $10528万
-$50,301/呎
+$44,667/呎
 (17年-01月-13日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 1437呎 (3房)
+          <t>C | 1722呎 (3房)
 -
 -
 (待售)</t>
@@ -18424,9 +18424,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 1709呎 (3房)
+          <t>D | 1722呎 (3房)
 $6300万
-$36,864/呎
+$36,585/呎
 (16年-09月-16日)</t>
         </is>
       </c>
@@ -18447,52 +18447,13 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 1070呎 (3房)
+          <t>B | 1083呎 (3房)
 $52262万
-$488,431/呎
+$482,568/呎
 (04年-11月-12日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52262万
-$488,431/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 879呎 (3房)
 $52262万
@@ -18500,202 +18461,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3280万
-$31,179/呎
-(26年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3680万
-$34,393/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2550万
-$29,825/呎
-(26年-02月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3467万
-$32,956/呎
-(16年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3130万
-$29,252/呎
-(11年-02月-21日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2866万
-$33,518/呎
-(15年-10月-19日)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2643万
-$30,917/呎
-(15年-11月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52262万
-$488,431/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3250万
-$30,374/呎
-(26年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2830万
-$33,099/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2620万
-$30,643/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52262万
-$488,431/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52262万
-$611,253/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 879呎 (3房)
 $52262万
@@ -18704,6 +18470,240 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$52262万
+$493,971/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$52262万
+$482,568/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$3280万
+$31,002/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$3680万
+$33,980/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$2550万
+$29,010/呎
+(26年-02月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$3467万
+$32,769/呎
+(16年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$3130万
+$28,901/呎
+(11年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$2866万
+$32,603/呎
+(15年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$2643万
+$30,073/呎
+(15年-11月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$52262万
+$493,971/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$52262万
+$482,568/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$3250万
+$30,009/呎
+(26年-03月-05日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$2830万
+$32,196/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$2620万
+$29,807/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$52262万
+$493,971/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$52262万
+$482,568/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
@@ -18712,9 +18712,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1058呎 (3房)
 $3426万
-$32,564/呎
+$32,380/呎
 (16年-10月-07日)</t>
         </is>
       </c>
@@ -18728,17 +18728,17 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2833万
-$33,133/呎
+$32,228/呎
 (16年-06月-14日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2640万
-$30,871/呎
+$30,028/呎
 (16年-11月-01日)</t>
         </is>
       </c>
@@ -18751,23 +18751,23 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1058呎 (3房)
 $3100万
-$29,468/呎
+$29,301/呎
 (26年-04月-29日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1070呎 (3房)
+          <t>B | 1083呎 (3房)
 $3418万
-$31,944/呎
+$31,560/呎
 (26年-04月-08日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 -
 -
 (待售)</t>
@@ -18775,9 +18775,9 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2430万
-$28,421/呎
+$27,645/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -18790,9 +18790,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $52262万
-$506,416/呎
+$503,004/呎
 (04年-11月-12日)</t>
         </is>
       </c>
@@ -18806,95 +18806,95 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
 (04年-11月-12日)</t>
         </is>
       </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $52262万
-$621,428/呎
+$604,186/呎
 (04年-11月-12日)</t>
         </is>
       </c>
@@ -18907,7 +18907,7 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 -
 -
 (待售)</t>
@@ -18915,15 +18915,15 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1064呎 (3房)
 $1269万
-$12,064/呎
+$11,928/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 -
 -
 (待售)</t>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 -
 -
 (待售)</t>
@@ -18946,31 +18946,31 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $3030万
-$29,360/呎
+$29,163/呎
 (26年-06月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1064呎 (3房)
 $1255万
-$11,931/呎
+$11,796/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2550万
-$30,321/呎
+$29,480/呎
 (26年-04月-14日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 -
 -
 (待售)</t>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 -
 -
 (待售)</t>
@@ -18993,15 +18993,15 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1064呎 (3房)
 $1305万
-$12,405/呎
+$12,265/呎
 (01年-12月-29日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 -
 -
 (待售)</t>
@@ -19009,9 +19009,9 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $1008万
-$11,994/呎
+$11,647/呎
 (01年-12月-29日)</t>
         </is>
       </c>
@@ -19024,17 +19024,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $3020万
-$29,264/呎
+$29,066/呎
 (26年-10月-20日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1064呎 (3房)
 $2750万
-$26,141/呎
+$25,846/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 -
 -
 (待售)</t>
@@ -19063,33 +19063,33 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $2280万
-$22,093/呎
+$21,944/呎
 (11年-01月-19日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1065呎 (3房)
+          <t>B | 1064呎 (3房)
 $2553万
-$23,972/呎
+$23,994/呎
 (11年-01月-12日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2578万
-$30,649/呎
+$29,798/呎
 (15年-10月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $2339万
-$27,842/呎
+$27,037/呎
 (16年-06月-08日)</t>
         </is>
       </c>
@@ -19102,130 +19102,13 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $52262万
-$506,416/呎
+$503,004/呎
 (04年-11月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2800万
-$26,616/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2350万
-$27,943/呎
-(26年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$889万
-$10,585/呎
-(02年-01月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 1064呎 (3房)
 $52262万
@@ -19233,7 +19116,7 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 865呎 (3房)
 $52262万
@@ -19241,89 +19124,206 @@
 (04年-11月-12日)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
 $52262万
-$622,168/呎
+$604,186/呎
 (04年-11月-12日)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52262万
-$496,788/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52262万
-$621,428/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52262万
-$622,168/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52262万
-$506,416/呎
-(04年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$2800万
+$26,316/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$2350万
+$27,168/呎
+(26年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
+$889万
+$10,279/呎
+(02年-01月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
+$52262万
+$604,186/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1039呎 (3房)
+$52262万
+$503,004/呎
+(04年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1056呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $894万
-$10,637/呎
+$10,329/呎
 (02年-02月-16日)</t>
         </is>
       </c>
@@ -19336,33 +19336,33 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 $998万
-$9,671/呎
+$9,605/呎
 (01年-12月-29日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $2680万
-$25,720/呎
+$25,379/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2370万
-$28,181/呎
+$27,399/呎
 (26年-07月-10日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $843万
-$10,032/呎
+$9,742/呎
 (01年-12月-29日)</t>
         </is>
       </c>
@@ -19375,7 +19375,7 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 1032呎 (3房)
+          <t>A | 1039呎 (3房)
 -
 -
 (待售)</t>
@@ -19391,17 +19391,17 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $52262万
-$621,428/呎
+$604,186/呎
 (04年-11月-12日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $52262万
-$622,168/呎
+$604,186/呎
 (04年-11月-12日)</t>
         </is>
       </c>
@@ -19414,33 +19414,33 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 620呎 (2房)
+          <t>A | 619呎 (2房)
 $550万
-$8,863/呎
+$8,877/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $2088万
-$20,038/呎
+$19,773/呎
 (11年-01月-18日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $1960万
-$23,306/呎
+$22,659/呎
 (11年-06月-17日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $760万
-$9,048/呎
+$8,786/呎
 (02年-01月-08日)</t>
         </is>
       </c>
@@ -19453,33 +19453,33 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
+          <t>A | 619呎 (2房)
 $465万
-$7,518/呎
+$7,506/呎
 (01年-12月-31日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $1049万
-$10,067/呎
+$9,934/呎
 (02年-03月-26日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2083万
-$24,774/呎
+$24,086/呎
 (15年-09月-29日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $1670万
-$19,881/呎
+$19,306/呎
 (11年-01月-24日)</t>
         </is>
       </c>
@@ -19492,33 +19492,33 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
+          <t>A | 619呎 (2房)
 $482万
-$7,799/呎
+$7,787/呎
 (01年-12月-28日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $2188万
-$20,998/呎
+$20,720/呎
 (11年-01月-21日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $881万
-$10,476/呎
+$10,185/呎
 (01年-12月-29日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $785万
-$9,345/呎
+$9,075/呎
 (01年-12月-29日)</t>
         </is>
       </c>
@@ -19531,33 +19531,33 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
+          <t>A | 619呎 (2房)
 $529万
-$8,560/呎
+$8,546/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $2210万
-$21,209/呎
+$20,928/呎
 (11年-03月-01日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2034万
-$24,186/呎
+$23,515/呎
 (16年-10月-14日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $690万
-$8,211/呎
+$7,973/呎
 (02年-02月-19日)</t>
         </is>
       </c>
@@ -19570,9 +19570,9 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
+          <t>A | 619呎 (2房)
 $520万
-$8,414/呎
+$8,401/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -19586,17 +19586,17 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2040万
-$24,257/呎
+$23,584/呎
 (16年-06月-14日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $730万
-$8,692/呎
+$8,440/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -19609,33 +19609,33 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
+          <t>A | 619呎 (2房)
 $433万
-$7,010/呎
+$6,998/呎
 (02年-01月-08日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $52262万
-$501,556/呎
+$494,906/呎
 (04年-11月-12日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $4719万
-$56,108/呎
+$54,551/呎
 (15年-12月-24日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $662万
-$7,883/呎
+$7,655/呎
 (01年-12月-31日)</t>
         </is>
       </c>
@@ -19649,17 +19649,17 @@
       <c r="B37" s="22" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1056呎 (3房)
 $2561万
-$24,579/呎
+$24,253/呎
 (15年-11月-20日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 867呎 (3房)
 $1911万
-$22,717/呎
+$22,036/呎
 (15年-11月-18日)</t>
         </is>
       </c>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 2010呎 (3房)
+          <t>A | 2295呎 (3房)
 -
 -
 (待售)</t>
@@ -19804,25 +19804,25 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 1995呎 (3房)
+          <t>B | 2299呎 (3房)
 $4300万
-$21,554/呎
+$18,704/呎
 (07年-06月-29日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 1366呎 (3房)
+          <t>C | 1722呎 (3房)
 $2963万
-$21,690/呎
+$17,206/呎
 (06年-08月-17日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 1366呎 (3房)
+          <t>D | 1722呎 (3房)
 $3330万
-$24,378/呎
+$19,338/呎
 (07年-08月-24日)</t>
         </is>
       </c>
@@ -19835,15 +19835,15 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 2181呎 (3房)
+          <t>A | 2201呎 (3房)
 $7618万
-$34,928/呎
+$34,610/呎
 (16年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2158呎 (3房)
+          <t>B | 2176呎 (3房)
 -
 -
 (待售)</t>
@@ -19851,17 +19851,17 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 1412呎 (3房)
+          <t>C | 1532呎 (3房)
 $2980万
-$21,105/呎
+$19,452/呎
 (07年-08月-23日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>D | 1412呎 (3房)
+          <t>D | 1532呎 (3房)
 $6110万
-$43,275/呎
+$39,885/呎
 (15年-09月-11日)</t>
         </is>
       </c>
@@ -19874,33 +19874,33 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $2900万
-$27,103/呎
+$26,777/呎
 (11年-03月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $3442万
-$32,721/呎
+$32,535/呎
 (16年-01月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2798万
-$32,722/呎
+$31,828/呎
 (15年-12月-28日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2410万
-$28,187/呎
+$27,418/呎
 (11年-05月-19日)</t>
         </is>
       </c>
@@ -19913,31 +19913,31 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $3750万
-$35,047/呎
+$34,626/呎
 (26年-09月-29日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $3300万
-$31,369/呎
+$31,191/呎
 (26年-04月-22日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2590万
-$30,292/呎
+$29,465/呎
 (26年-04月-01日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 -
 -
 (待售)</t>
@@ -19952,15 +19952,15 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $1363万
-$12,738/呎
+$12,585/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 -
 -
 (待售)</t>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 -
 -
 (待售)</t>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 -
 -
 (待售)</t>
@@ -19991,33 +19991,33 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $3860万
-$36,075/呎
+$35,642/呎
 (17年-07月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $2789万
-$26,510/呎
+$26,359/呎
 (11年-06月-28日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2511万
-$29,371/呎
+$28,569/呎
 (11年-06月-28日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2850万
-$33,333/呎
+$32,423/呎
 (17年-08月-01日)</t>
         </is>
       </c>
@@ -20030,33 +20030,33 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $2925万
-$27,336/呎
+$27,008/呎
 (11年-06月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $2663万
-$25,312/呎
+$25,168/呎
 (11年-04月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2700万
-$31,579/呎
+$30,717/呎
 (26年-06月-02日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2630万
-$30,760/呎
+$29,920/呎
 (26年-04月-08日)</t>
         </is>
       </c>
@@ -20069,33 +20069,33 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $2650万
-$24,766/呎
+$24,469/呎
 (10年-12月-31日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $2580万
-$24,525/呎
+$24,386/呎
 (11年-01月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2685万
-$31,399/呎
+$30,542/呎
 (15年-12月-02日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2619万
-$30,628/呎
+$29,792/呎
 (15年-11月-12日)</t>
         </is>
       </c>
@@ -20116,25 +20116,25 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $2520万
-$23,954/呎
+$23,819/呎
 (11年-01月-13日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $4719万
-$55,189/呎
+$53,682/呎
 (15年-12月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2602万
-$30,436/呎
+$29,605/呎
 (15年-11月-09日)</t>
         </is>
       </c>
@@ -20147,33 +20147,33 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 $2715万
-$25,374/呎
+$25,069/呎
 (11年-01月-24日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 $3372万
-$32,055/呎
+$31,874/呎
 (16年-06月-22日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 $2685万
-$31,399/呎
+$30,542/呎
 (15年-09月-30日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $2265万
-$26,491/呎
+$25,768/呎
 (11年-01月-24日)</t>
         </is>
       </c>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1070呎 (3房)
+          <t>A | 1083呎 (3房)
 -
 -
 (待售)</t>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1052呎 (3房)
+          <t>B | 1058呎 (3房)
 -
 -
 (待售)</t>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 855呎 (3房)
+          <t>C | 879呎 (3房)
 -
 -
 (待售)</t>
@@ -20210,9 +20210,9 @@
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>D | 855呎 (3房)
+          <t>D | 879呎 (3房)
 $988万
-$11,557/呎
+$11,241/呎
 (02年-01月-09日)</t>
         </is>
       </c>
@@ -20225,33 +20225,33 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $3376万
-$32,095/呎
+$31,733/呎
 (16年-06月-14日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $2448万
-$23,721/呎
+$23,561/呎
 (11年-05月-30日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $1792万
-$21,307/呎
+$20,716/呎
 (08年-03月-27日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2560万
-$30,440/呎
+$29,595/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -20264,33 +20264,33 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1192万
-$11,335/呎
+$11,207/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $2250万
-$21,802/呎
+$21,655/呎
 (11年-01月-17日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2080万
-$24,732/呎
+$24,046/呎
 (11年-01月-27日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2154万
-$25,612/呎
+$24,902/呎
 (11年-06月-02日)</t>
         </is>
       </c>
@@ -20303,23 +20303,23 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 1065呎 (3房)
+          <t>A | 1064呎 (3房)
 $2350万
-$22,066/呎
+$22,086/呎
 (11年-01月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $2210万
-$21,415/呎
+$21,270/呎
 (11年-01月-17日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 -
 -
 (待售)</t>
@@ -20342,33 +20342,33 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1167万
-$11,093/呎
+$10,968/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $2160万
-$20,930/呎
+$20,789/呎
 (11年-01月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 841呎 (3房)
+          <t>C | 865呎 (3房)
 $2083万
-$24,768/呎
+$24,081/呎
 (11年-03月-09日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2118万
-$25,184/呎
+$24,486/呎
 (11年-06月-14日)</t>
         </is>
       </c>
@@ -20381,33 +20381,33 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1210万
-$11,507/呎
+$11,377/呎
 (02年-01月-17日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1038呎 (3房)
+          <t>B | 1039呎 (3房)
 $2160万
-$20,809/呎
+$20,789/呎
 (11年-01月-07日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1960万
-$23,333/呎
+$22,659/呎
 (11年-01月-19日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2380万
-$28,299/呎
+$27,513/呎
 (15年-11月-06日)</t>
         </is>
       </c>
@@ -20420,33 +20420,33 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1197万
-$11,378/呎
+$11,250/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $3028万
-$29,341/呎
+$29,143/呎
 (26年-08月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1990万
-$23,690/呎
+$23,006/呎
 (11年-01月-24日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2000万
-$23,781/呎
+$23,121/呎
 (11年-03月-17日)</t>
         </is>
       </c>
@@ -20467,25 +20467,25 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $2100万
-$20,349/呎
+$20,212/呎
 (11年-01月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1900万
-$22,619/呎
+$21,965/呎
 (11年-01月-14日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $946万
-$11,253/呎
+$10,941/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -20498,33 +20498,33 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1140万
-$10,833/呎
+$10,711/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1038呎 (3房)
+          <t>B | 1039呎 (3房)
 $2140万
-$20,617/呎
+$20,597/呎
 (11年-01月-17日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1990万
-$23,690/呎
+$23,006/呎
 (11年-01月-31日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $2363万
-$28,103/呎
+$27,323/呎
 (15年-11月-13日)</t>
         </is>
       </c>
@@ -20537,23 +20537,23 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1015万
-$9,651/呎
+$9,542/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $953万
-$9,232/呎
+$9,169/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 -
 -
 (待售)</t>
@@ -20561,9 +20561,9 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $946万
-$11,249/呎
+$10,936/呎
 (02年-01月-10日)</t>
         </is>
       </c>
@@ -20576,23 +20576,23 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1052呎 (3房)
+          <t>A | 1064呎 (3房)
 $1064万
-$10,113/呎
+$9,999/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $1950万
-$18,895/呎
+$18,768/呎
 (10年-12月-31日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 -
 -
 (待售)</t>
@@ -20600,9 +20600,9 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $896万
-$10,649/呎
+$10,354/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -20623,25 +20623,25 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $1938万
-$18,779/呎
+$18,653/呎
 (11年-01月-14日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>C | 863呎 (2房)
+          <t>C | 865呎 (2房)
 $1810万
-$20,973/呎
+$20,925/呎
 (11年-01月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $1838万
-$21,855/呎
+$21,249/呎
 (11年-02月-01日)</t>
         </is>
       </c>
@@ -20662,25 +20662,25 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $1900万
-$18,411/呎
+$18,287/呎
 (10年-12月-29日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1740万
-$20,714/呎
+$20,116/呎
 (11年-01月-12日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $1790万
-$21,284/呎
+$20,694/呎
 (11年-01月-24日)</t>
         </is>
       </c>
@@ -20693,17 +20693,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 1065呎 (3房)
+          <t>A | 1064呎 (3房)
 $942万
-$8,848/呎
+$8,856/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $1867万
-$18,094/呎
+$17,972/呎
 (10年-12月-20日)</t>
         </is>
       </c>
@@ -20717,9 +20717,9 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $913万
-$10,856/呎
+$10,555/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -20732,33 +20732,33 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $1065万
-$10,221/呎
+$10,085/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $1918万
-$18,585/呎
+$18,460/呎
 (11年-01月-06日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $881万
-$10,492/呎
+$10,188/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 $733万
-$8,721/呎
+$8,479/呎
 (02年-01月-08日)</t>
         </is>
       </c>
@@ -20771,9 +20771,9 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $1015万
-$9,740/呎
+$9,611/呎
 (02年-03月-16日)</t>
         </is>
       </c>
@@ -20787,15 +20787,15 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $1780万
-$21,190/呎
+$20,578/呎
 (11年-01月-21日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>D | 841呎 (3房)
+          <t>D | 865呎 (3房)
 -
 -
 (待售)</t>
@@ -20818,17 +20818,17 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 1032呎 (3房)
+          <t>B | 1039呎 (3房)
 $840万
-$8,140/呎
+$8,085/呎
 (01年-12月-29日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $750万
-$8,935/呎
+$8,676/呎
 (02年-01月-09日)</t>
         </is>
       </c>
@@ -20849,33 +20849,33 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $858万
-$8,234/呎
+$8,125/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 618呎 (2房)
+          <t>B | 619呎 (2房)
 $487万
-$7,880/呎
+$7,868/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $791万
-$9,417/呎
+$9,145/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (2房)
+          <t>D | 865呎 (2房)
 $733万
-$8,717/呎
+$8,475/呎
 (02年-01月-10日)</t>
         </is>
       </c>
@@ -20888,9 +20888,9 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $891万
-$8,548/呎
+$8,435/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -20904,17 +20904,17 @@
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $723万
-$8,607/呎
+$8,358/呎
 (02年-01月-08日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>D | 841呎 (2房)
+          <t>D | 865呎 (2房)
 $715万
-$8,501/呎
+$8,265/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -20927,25 +20927,25 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $828万
-$7,947/呎
+$7,842/呎
 (01年-12月-28日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>B | 618呎 (2房)
+          <t>B | 619呎 (2房)
 $481万
-$7,783/呎
+$7,771/呎
 (01年-12月-28日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $709万
-$8,445/呎
+$8,201/呎
 (01年-12月-28日)</t>
         </is>
       </c>
@@ -20966,33 +20966,33 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $866万
-$8,311/呎
+$8,201/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>B | 618呎 (2房)
+          <t>B | 619呎 (2房)
 $426万
-$6,893/呎
+$6,882/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $650万
-$7,736/呎
+$7,512/呎
 (02年-01月-09日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $1490万
-$17,738/呎
+$17,225/呎
 (11年-01月-17日)</t>
         </is>
       </c>
@@ -21013,25 +21013,25 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>B | 618呎 (2房)
+          <t>B | 619呎 (2房)
 $456万
-$7,385/呎
+$7,373/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $724万
-$8,625/呎
+$8,376/呎
 (02年-01月-02日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $718万
-$8,548/呎
+$8,301/呎
 (02年-01月-02日)</t>
         </is>
       </c>
@@ -21044,33 +21044,33 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $760万
-$7,295/呎
+$7,198/呎
 (02年-01月-10日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>B | 618呎 (2房)
+          <t>B | 619呎 (2房)
 $373万
-$6,042/呎
+$6,032/呎
 (01年-12月-31日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>C | 840呎 (2房)
+          <t>C | 865呎 (2房)
 $707万
-$8,417/呎
+$8,173/呎
 (01年-12月-29日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 865呎 (2房)
 $667万
-$7,936/呎
+$7,706/呎
 (01年-12月-29日)</t>
         </is>
       </c>
@@ -21083,9 +21083,9 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>A | 1042呎 (3房)
+          <t>A | 1056呎 (3房)
 $732万
-$7,022/呎
+$6,929/呎
 (01年-12月-29日)</t>
         </is>
       </c>
@@ -21093,9 +21093,9 @@
       <c r="D38" s="22" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>D | 840呎 (2房)
+          <t>D | 867呎 (2房)
 $662万
-$7,875/呎
+$7,630/呎
 (02年-01月-10日)</t>
         </is>
       </c>
